--- a/samples/Product Launch Model.xlsx
+++ b/samples/Product Launch Model.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e2453df3e28d0d9/04 - Projects/MonteCarlo.XL/samples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{6CE13CD2-F145-4686-82EE-1CECA8270112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45CBCABE-A736-4F79-B067-6A85935C5992}"/>
+  <xr:revisionPtr revIDLastSave="4527" documentId="8_{6CE13CD2-F145-4686-82EE-1CECA8270112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EC4F07E-EE3E-4347-811A-F2A45FF398B3}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DE2A6105-9CAF-4ED7-AB3C-AA8D1A93A4D9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{DE2A6105-9CAF-4ED7-AB3C-AA8D1A93A4D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Launch Model" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="MC Results — Net Profit ($)" sheetId="3" r:id="rId3"/>
+    <sheet name="MC Results — Net Profit ($) (2)" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="107">
   <si>
     <t>NEW PRODUCT LAUNCH - COST &amp; REVENUE MODEL</t>
   </si>
@@ -208,16 +210,167 @@
   </si>
   <si>
     <t xml:space="preserve">  Binomial   - competitor entry (yes/no event)</t>
+  </si>
+  <si>
+    <t>MonteCarlo.XL Simulation Results</t>
+  </si>
+  <si>
+    <t>Output: Net Profit ($)</t>
+  </si>
+  <si>
+    <t>Iterations: 5,000</t>
+  </si>
+  <si>
+    <t>Date: 2026-04-19</t>
+  </si>
+  <si>
+    <t>SUMMARY STATISTICS</t>
+  </si>
+  <si>
+    <t>Statistic</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>Std Dev</t>
+  </si>
+  <si>
+    <t>Variance</t>
+  </si>
+  <si>
+    <t>Minimum</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>Skewness</t>
+  </si>
+  <si>
+    <t>Kurtosis</t>
+  </si>
+  <si>
+    <t>PERCENTILES</t>
+  </si>
+  <si>
+    <t>Percentile</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>P5</t>
+  </si>
+  <si>
+    <t>P10</t>
+  </si>
+  <si>
+    <t>P25</t>
+  </si>
+  <si>
+    <t>P50</t>
+  </si>
+  <si>
+    <t>P75</t>
+  </si>
+  <si>
+    <t>P90</t>
+  </si>
+  <si>
+    <t>P95</t>
+  </si>
+  <si>
+    <t>P99</t>
+  </si>
+  <si>
+    <t>SENSITIVITY (TOP 7 INPUTS)</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Rank Corr</t>
+  </si>
+  <si>
+    <t>Swing</t>
+  </si>
+  <si>
+    <t>% Variance</t>
+  </si>
+  <si>
+    <t>INPUT ASSUMPTIONS</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>Product Launch Model!B6</t>
+  </si>
+  <si>
+    <t>Product Launch Model!B8</t>
+  </si>
+  <si>
+    <t>Normal(μ=45, σ=5)</t>
+  </si>
+  <si>
+    <t>Product Launch Model!B12</t>
+  </si>
+  <si>
+    <t>Binomial</t>
+  </si>
+  <si>
+    <t>Product Launch Model!B11</t>
+  </si>
+  <si>
+    <t>Poisson</t>
+  </si>
+  <si>
+    <t>Product Launch Model!B7</t>
+  </si>
+  <si>
+    <t>Lognormal(μ=9.2, σ=0.4)</t>
+  </si>
+  <si>
+    <t>Product Launch Model!B10</t>
+  </si>
+  <si>
+    <t>Beta</t>
+  </si>
+  <si>
+    <t>Product Launch Model!B9</t>
+  </si>
+  <si>
+    <t>PERT(50000, 80000, 150000)</t>
+  </si>
+  <si>
+    <t>Bin</t>
+  </si>
+  <si>
+    <t>Relative Frequency</t>
+  </si>
+  <si>
+    <t>P10 Impact</t>
+  </si>
+  <si>
+    <t>P90 Impact</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="9"/>
       <color theme="1"/>
@@ -265,8 +418,21 @@
       <name val="Aptos Serif"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Serif"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -276,12 +442,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCF2FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFE2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -309,8 +469,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCFCE7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F8FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -318,35 +490,56 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFE2E8E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -362,6 +555,830 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Net Profit ($) Distribution</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Relative Frequency</c:v>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'MC Results — Net Profit ($) (2)'!$AA$2:$AA$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>-288394.46390262153</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-263347.24196587235</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-238300.02002912312</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-213252.79809237388</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-188205.57615562464</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-163158.35421887541</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-138111.1322821262</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-113063.91034537696</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-88016.688408627728</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-62969.466471878492</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-37922.244535129255</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-12875.022598380048</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12172.199338369159</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37219.421275118395</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>62266.643211867631</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>87313.865148616867</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>112361.0870853661</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>137408.30902211534</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>162455.53095886458</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>187502.75289561381</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>212549.97483236302</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>237597.19676911226</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>262644.41870586149</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>287691.64064261067</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>312738.86257935991</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>337786.08451610914</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>362833.30645285838</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>387880.52838960761</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>412927.75032635685</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>437974.97226310609</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>463022.19419985532</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>488069.41613660456</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>513116.63807335374</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>538163.86001010297</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>563211.08194685215</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>588258.30388360145</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>613305.52582035074</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>638352.74775709992</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>663399.9696938491</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>688447.19163059839</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>713494.41356734768</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>738541.63550409675</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>763588.85744084604</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>788636.07937759534</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>813683.30131434451</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>838730.52325109369</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>863777.74518784299</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>888824.96712459216</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>913872.18906134134</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>938919.41099809064</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'MC Results — Net Profit ($) (2)'!$AB$2:$AB$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>3.2000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.7999999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.0400000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.2599999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.9400000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.6200000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.2600000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.3200000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.4200000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.8600000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.7200000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.5600000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.8399999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.8800000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.98E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.64E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.5599999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.6199999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.2200000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.1999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.1999999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.8E-3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.2000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.8E-3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.6000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.1999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.1999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4.0000000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>8.0000000000000004E-4</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5.9999999999999995E-4</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>8.0000000000000004E-4</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>4.0000000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>4.0000000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4.0000000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2.0000000000000001E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D9BE-4C77-A36E-0A2A48566939}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="499009568"/>
+        <c:axId val="499010048"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="499009568"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Output value</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="499010048"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="499010048"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Relative frequency</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0.0%" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="499009568"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sensitivity</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Input P10</c:v>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'MC Results — Net Profit ($) (2)'!$AD$2:$AD$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Defect Rate</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Dev Delay (months)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Marketing Spend ($)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Unit Mfg Cost ($)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Competitor Enters? (0/1)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Selling Price ($)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Units Sold (Year 1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'MC Results — Net Profit ($) (2)'!$AE$2:$AE$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>43489.202695485619</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43840.743281677729</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>48749.950121117916</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>55760.680715506562</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>49135.567208000924</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-63016.722614992206</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-116061.43867185959</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-13BE-4CFC-84EB-C0C000CB4E50}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Input P90</c:v>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'MC Results — Net Profit ($) (2)'!$AD$2:$AD$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Defect Rate</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Dev Delay (months)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Marketing Spend ($)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Unit Mfg Cost ($)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Competitor Enters? (0/1)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Selling Price ($)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Units Sold (Year 1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'MC Results — Net Profit ($) (2)'!$AF$2:$AF$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>9491.912847061707</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-8611.4666470377124</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-18121.598763323811</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-12481.589280487315</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-22273.370521482604</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>104318.68343506276</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>265478.14778783626</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-13BE-4CFC-84EB-C0C000CB4E50}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="642220608"/>
+        <c:axId val="642223008"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="642220608"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="642223008"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="642223008"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Change from median output</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="642220608"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7763A149-2722-E52C-21D7-6A2F9DB3DE80}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>476249</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>466724</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5817755-1D0F-0C40-4171-62ABDAE0E8F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -692,24 +1709,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -731,7 +1748,7 @@
       <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="15" t="s">
         <v>37</v>
       </c>
     </row>
@@ -739,14 +1756,13 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="23">
-        <f>_xll.MC.Triangular(12, 15, 22)</f>
+      <c r="B6" s="17">
         <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="15" t="s">
         <v>38</v>
       </c>
     </row>
@@ -754,14 +1770,13 @@
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6">
-        <f>_xll.MC.Lognormal(9.2, 0.4)</f>
+      <c r="B7" s="17">
         <v>10721.431916447313</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="15" t="s">
         <v>39</v>
       </c>
     </row>
@@ -769,14 +1784,13 @@
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="6">
-        <f>_xll.MC.Normal(45, 5)</f>
-        <v>45</v>
+      <c r="B8" s="17">
+        <v>55</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="15" t="s">
         <v>40</v>
       </c>
     </row>
@@ -784,14 +1798,13 @@
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="7">
-        <f>_xll.MC.PERT(50000, 80000, 150000)</f>
+      <c r="B9" s="19">
         <v>80000</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="15" t="s">
         <v>41</v>
       </c>
     </row>
@@ -799,14 +1812,13 @@
       <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="8">
-        <f>_xll.MC.Beta(2, 50)</f>
+      <c r="B10" s="18">
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="15" t="s">
         <v>42</v>
       </c>
     </row>
@@ -814,14 +1826,13 @@
       <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="6">
-        <f>_xll.MC.Poisson(2)</f>
+      <c r="B11" s="17">
         <v>2</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="15" t="s">
         <v>43</v>
       </c>
     </row>
@@ -829,29 +1840,28 @@
       <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="6">
-        <f>_xll.MC.Binomial(1, 0.3)</f>
+      <c r="B12" s="17">
         <v>0.3</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="E14" s="20" t="s">
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="E14" s="15" t="s">
         <v>46</v>
       </c>
     </row>
@@ -859,19 +1869,19 @@
       <c r="A15" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="8">
         <v>200000</v>
       </c>
-      <c r="E15" s="20"/>
+      <c r="E15" s="15"/>
     </row>
     <row r="16" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="8">
         <v>15000</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="15" t="s">
         <v>47</v>
       </c>
     </row>
@@ -879,23 +1889,23 @@
       <c r="A17" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="9">
         <v>0.15</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="E18" s="20"/>
+      <c r="E18" s="15"/>
     </row>
     <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="E19" s="20" t="s">
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="E19" s="15" t="s">
         <v>49</v>
       </c>
     </row>
@@ -903,11 +1913,11 @@
       <c r="A20" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="12">
         <f>B8 * (1 - B12 * B17)</f>
-        <v>42.975000000000001</v>
-      </c>
-      <c r="E20" s="20" t="s">
+        <v>52.524999999999999</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>50</v>
       </c>
     </row>
@@ -915,11 +1925,11 @@
       <c r="A21" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="8">
         <f>B20 * B7</f>
-        <v>460753.53660932329</v>
-      </c>
-      <c r="E21" s="20" t="s">
+        <v>563143.21141139511</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>51</v>
       </c>
     </row>
@@ -927,11 +1937,11 @@
       <c r="A22" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="8">
         <f>B6 * B7</f>
         <v>160821.4787467097</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -939,14 +1949,14 @@
       <c r="A23" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="8">
         <f>B10 * B22 * 2</f>
         <v>12370.882980516131</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="15" t="s">
         <v>53</v>
       </c>
     </row>
@@ -954,11 +1964,11 @@
       <c r="A24" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="8">
         <f>B11 * B16</f>
         <v>30000</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="15" t="s">
         <v>54</v>
       </c>
     </row>
@@ -966,51 +1976,51 @@
       <c r="A25" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="8">
         <f>B22 + B9 + B15 + B23 + B24</f>
         <v>483192.36172722583</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="15" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="15" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
     </row>
     <row r="28" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28" s="20">
         <f>B21 - B25</f>
-        <v>-22438.825117902539</v>
+        <v>79950.849684169283</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="21">
         <f>B28 / B25</f>
-        <v>-4.6438699977980648E-2</v>
+        <v>0.16546381113802361</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="20">
         <f>(B9 + B15 + B24) / (B20 - B6)</f>
-        <v>11081.322609472743</v>
+        <v>8261.159227181879</v>
       </c>
     </row>
   </sheetData>
@@ -1028,6 +2038,1245 @@
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CFEA44-46EE-4DC9-BEFC-2E96467A889A}">
+  <sheetPr>
+    <tabColor rgb="FF3B82F6"/>
+  </sheetPr>
+  <dimension ref="A1:D46"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="8">
+        <v>-45633.591617295977</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="27">
+        <v>-70405.669457712385</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="8">
+        <v>134256.93599994632</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="27">
+        <v>18024924864.093685</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="8">
+        <v>-327788.07269815181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="27">
+        <v>925080.02497914166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="28">
+        <v>1.3041462247573139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="29">
+        <v>3.1768447413114185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A16" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="27">
+        <v>-258520.850631034</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="8">
+        <v>-215498.24664480478</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="27">
+        <v>-187914.98924327106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="8">
+        <v>-138436.55440709915</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="27">
+        <v>-70405.669457712385</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="8">
+        <v>19697.814235958343</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="27">
+        <v>127625.69898171865</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="8">
+        <v>210374.86818804356</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="27">
+        <v>371543.33275390184</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A28" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="32">
+        <v>0.79295548112621927</v>
+      </c>
+      <c r="C30" s="27">
+        <v>379168.09846502478</v>
+      </c>
+      <c r="D30" s="33">
+        <v>0.68598689193502271</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="30">
+        <v>0.35635523025420923</v>
+      </c>
+      <c r="C31" s="8">
+        <v>164296.87625888357</v>
+      </c>
+      <c r="D31" s="31">
+        <v>0.1385429660023092</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="32">
+        <v>-0.25498572396856189</v>
+      </c>
+      <c r="C32" s="27">
+        <v>71111.708391492066</v>
+      </c>
+      <c r="D32" s="33">
+        <v>7.0933263010010891E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="30">
+        <v>-0.18430700489707785</v>
+      </c>
+      <c r="C33" s="8">
+        <v>68441.328839607144</v>
+      </c>
+      <c r="D33" s="31">
+        <v>3.7059699162448799E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="32">
+        <v>-0.16951487890859515</v>
+      </c>
+      <c r="C34" s="27">
+        <v>81940.730041364644</v>
+      </c>
+      <c r="D34" s="33">
+        <v>3.1349733535240072E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="30">
+        <v>-0.16817506810300273</v>
+      </c>
+      <c r="C35" s="8">
+        <v>71606.032991691463</v>
+      </c>
+      <c r="D35" s="31">
+        <v>3.0856128235143929E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="32">
+        <v>-6.9510515612420623E-2</v>
+      </c>
+      <c r="C36" s="27">
+        <v>31904.761893440678</v>
+      </c>
+      <c r="D36" s="33">
+        <v>5.2713181198246143E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="26" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" s="26" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172396A9-7C70-499E-B712-32D3A00A667E}">
+  <sheetPr>
+    <tabColor rgb="FF3B82F6"/>
+  </sheetPr>
+  <dimension ref="A1:AF51"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA2">
+        <v>-288394.46390262153</v>
+      </c>
+      <c r="AB2">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE2">
+        <v>43489.202695485619</v>
+      </c>
+      <c r="AF2">
+        <v>9491.912847061707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA3">
+        <v>-263347.24196587235</v>
+      </c>
+      <c r="AB3">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE3">
+        <v>43840.743281677729</v>
+      </c>
+      <c r="AF3">
+        <v>-8611.4666470377124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AA4">
+        <v>-238300.02002912312</v>
+      </c>
+      <c r="AB4">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE4">
+        <v>48749.950121117916</v>
+      </c>
+      <c r="AF4">
+        <v>-18121.598763323811</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="AA5">
+        <v>-213252.79809237388</v>
+      </c>
+      <c r="AB5">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE5">
+        <v>55760.680715506562</v>
+      </c>
+      <c r="AF5">
+        <v>-12481.589280487315</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A6" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA6">
+        <v>-188205.57615562464</v>
+      </c>
+      <c r="AB6">
+        <v>5.9400000000000001E-2</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE6">
+        <v>49135.567208000924</v>
+      </c>
+      <c r="AF6">
+        <v>-22273.370521482604</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="8">
+        <v>-44943.777159962214</v>
+      </c>
+      <c r="AA7">
+        <v>-163158.35421887541</v>
+      </c>
+      <c r="AB7">
+        <v>7.6200000000000004E-2</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE7">
+        <v>-63016.722614992206</v>
+      </c>
+      <c r="AF7">
+        <v>104318.68343506276</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A8" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="27">
+        <v>-69777.648264224204</v>
+      </c>
+      <c r="AA8">
+        <v>-138111.1322821262</v>
+      </c>
+      <c r="AB8">
+        <v>8.2600000000000007E-2</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE8">
+        <v>-116061.43867185959</v>
+      </c>
+      <c r="AF8">
+        <v>265478.14778783626</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="8">
+        <v>135723.23195916024</v>
+      </c>
+      <c r="AA9">
+        <v>-113063.91034537696</v>
+      </c>
+      <c r="AB9">
+        <v>9.3200000000000005E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A10" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="27">
+        <v>18420795693.440018</v>
+      </c>
+      <c r="AA10">
+        <v>-88016.688408627728</v>
+      </c>
+      <c r="AB10">
+        <v>9.4200000000000006E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="8">
+        <v>-300918.07487099618</v>
+      </c>
+      <c r="AA11">
+        <v>-62969.466471878492</v>
+      </c>
+      <c r="AB11">
+        <v>7.8600000000000003E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A12" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="27">
+        <v>951443.0219664654</v>
+      </c>
+      <c r="AA12">
+        <v>-37922.244535129255</v>
+      </c>
+      <c r="AB12">
+        <v>7.7200000000000005E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="28">
+        <v>1.4378010443869675</v>
+      </c>
+      <c r="AA13">
+        <v>-12875.022598380048</v>
+      </c>
+      <c r="AB13">
+        <v>6.5600000000000006E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A14" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="29">
+        <v>4.1335101804052981</v>
+      </c>
+      <c r="AA14">
+        <v>12172.199338369159</v>
+      </c>
+      <c r="AB14">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AA15">
+        <v>37219.421275118395</v>
+      </c>
+      <c r="AB15">
+        <v>3.8399999999999997E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A16" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="AA16">
+        <v>62266.643211867631</v>
+      </c>
+      <c r="AB16">
+        <v>3.8800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A17" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA17">
+        <v>87313.865148616867</v>
+      </c>
+      <c r="AB17">
+        <v>2.98E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A18" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="27">
+        <v>-258370.62867506244</v>
+      </c>
+      <c r="AA18">
+        <v>112361.0870853661</v>
+      </c>
+      <c r="AB18">
+        <v>2.64E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="8">
+        <v>-213555.51374822253</v>
+      </c>
+      <c r="AA19">
+        <v>137408.30902211534</v>
+      </c>
+      <c r="AB19">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A20" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="27">
+        <v>-189674.63388576766</v>
+      </c>
+      <c r="AA20">
+        <v>162455.53095886458</v>
+      </c>
+      <c r="AB20">
+        <v>1.5599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="8">
+        <v>-138804.81572120718</v>
+      </c>
+      <c r="AA21">
+        <v>187502.75289561381</v>
+      </c>
+      <c r="AB21">
+        <v>1.6199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A22" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="27">
+        <v>-69777.648264224204</v>
+      </c>
+      <c r="AA22">
+        <v>212549.97483236302</v>
+      </c>
+      <c r="AB22">
+        <v>1.2200000000000001E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="8">
+        <v>18386.249207971559</v>
+      </c>
+      <c r="AA23">
+        <v>237597.19676911226</v>
+      </c>
+      <c r="AB23">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A24" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="27">
+        <v>128300.84459139135</v>
+      </c>
+      <c r="AA24">
+        <v>262644.41870586149</v>
+      </c>
+      <c r="AB24">
+        <v>6.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="8">
+        <v>205700.73600518837</v>
+      </c>
+      <c r="AA25">
+        <v>287691.64064261067</v>
+      </c>
+      <c r="AB25">
+        <v>4.1999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A26" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="27">
+        <v>390037.01291265443</v>
+      </c>
+      <c r="AA26">
+        <v>312738.86257935991</v>
+      </c>
+      <c r="AB26">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AA27">
+        <v>337786.08451610914</v>
+      </c>
+      <c r="AB27">
+        <v>2.8E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A28" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="AA28">
+        <v>362833.30645285838</v>
+      </c>
+      <c r="AB28">
+        <v>3.2000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A29" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA29">
+        <v>387880.52838960761</v>
+      </c>
+      <c r="AB29">
+        <v>1.8E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A30" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="32">
+        <v>0.79395662350226492</v>
+      </c>
+      <c r="C30" s="27">
+        <v>381539.58645969589</v>
+      </c>
+      <c r="D30" s="33">
+        <v>0.68570835893241944</v>
+      </c>
+      <c r="AA30">
+        <v>412927.75032635685</v>
+      </c>
+      <c r="AB30">
+        <v>1.6000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="30">
+        <v>0.36629019778760791</v>
+      </c>
+      <c r="C31" s="8">
+        <v>167335.40605005497</v>
+      </c>
+      <c r="D31" s="31">
+        <v>0.14594744110878027</v>
+      </c>
+      <c r="AA31">
+        <v>437974.97226310609</v>
+      </c>
+      <c r="AB31">
+        <v>1.1999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A32" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="32">
+        <v>-0.27432601525346068</v>
+      </c>
+      <c r="C32" s="27">
+        <v>71408.937729483529</v>
+      </c>
+      <c r="D32" s="33">
+        <v>8.1861534584462672E-2</v>
+      </c>
+      <c r="AA32">
+        <v>463022.19419985532</v>
+      </c>
+      <c r="AB32">
+        <v>1.1999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="30">
+        <v>-0.17898059688722387</v>
+      </c>
+      <c r="C33" s="8">
+        <v>68242.269995993876</v>
+      </c>
+      <c r="D33" s="31">
+        <v>3.4846390212692445E-2</v>
+      </c>
+      <c r="AA33">
+        <v>488069.41613660456</v>
+      </c>
+      <c r="AB33">
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A34" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="32">
+        <v>-0.15215859181434369</v>
+      </c>
+      <c r="C34" s="27">
+        <v>66871.548884441727</v>
+      </c>
+      <c r="D34" s="33">
+        <v>2.5184820048916076E-2</v>
+      </c>
+      <c r="AA34">
+        <v>513116.63807335374</v>
+      </c>
+      <c r="AB34">
+        <v>8.0000000000000004E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="30">
+        <v>-0.14235193154300302</v>
+      </c>
+      <c r="C35" s="8">
+        <v>52452.209928715441</v>
+      </c>
+      <c r="D35" s="31">
+        <v>2.2043097425892499E-2</v>
+      </c>
+      <c r="AA35">
+        <v>538163.86001010297</v>
+      </c>
+      <c r="AB35">
+        <v>5.9999999999999995E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A36" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="32">
+        <v>-6.365982888239316E-2</v>
+      </c>
+      <c r="C36" s="27">
+        <v>33997.289848423912</v>
+      </c>
+      <c r="D36" s="33">
+        <v>4.4083576868366716E-3</v>
+      </c>
+      <c r="AA36">
+        <v>563211.08194685215</v>
+      </c>
+      <c r="AB36">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AA37">
+        <v>588258.30388360145</v>
+      </c>
+      <c r="AB37">
+        <v>8.0000000000000004E-4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="AA38">
+        <v>613305.52582035074</v>
+      </c>
+      <c r="AB38">
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A39" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA39">
+        <v>638352.74775709992</v>
+      </c>
+      <c r="AB39">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A40" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA40">
+        <v>663399.9696938491</v>
+      </c>
+      <c r="AB40">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA41">
+        <v>688447.19163059839</v>
+      </c>
+      <c r="AB41">
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A42" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA42">
+        <v>713494.41356734768</v>
+      </c>
+      <c r="AB42">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA43">
+        <v>738541.63550409675</v>
+      </c>
+      <c r="AB43">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A44" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA44">
+        <v>763588.85744084604</v>
+      </c>
+      <c r="AB44">
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA45">
+        <v>788636.07937759534</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A46" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA46">
+        <v>813683.30131434451</v>
+      </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AA47">
+        <v>838730.52325109369</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AA48">
+        <v>863777.74518784299</v>
+      </c>
+      <c r="AB48">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="49" spans="27:28" x14ac:dyDescent="0.2">
+      <c r="AA49">
+        <v>888824.96712459216</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="27:28" x14ac:dyDescent="0.2">
+      <c r="AA50">
+        <v>913872.18906134134</v>
+      </c>
+      <c r="AB50">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="51" spans="27:28" x14ac:dyDescent="0.2">
+      <c r="AA51">
+        <v>938919.41099809064</v>
+      </c>
+      <c r="AB51">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1048,9 +3297,85 @@
         "mode": 15,
         "max": 22
       }
+    },
+    {
+      "sheetName": "Product Launch Model",
+      "cellAddress": "B8",
+      "label": "Selling Price ($)",
+      "distributionName": "Normal",
+      "parameters": {
+        "mean": 45,
+        "stdDev": 5
+      }
+    },
+    {
+      "sheetName": "Product Launch Model",
+      "cellAddress": "B12",
+      "label": "Competitor Enters? (0/1)",
+      "distributionName": "Binomial",
+      "parameters": {
+        "n": 1,
+        "p": 0.3
+      }
+    },
+    {
+      "sheetName": "Product Launch Model",
+      "cellAddress": "B11",
+      "label": "Dev Delay (months)",
+      "distributionName": "Poisson",
+      "parameters": {
+        "lambda": 2
+      }
+    },
+    {
+      "sheetName": "Product Launch Model",
+      "cellAddress": "B7",
+      "label": "Units Sold (Year 1)",
+      "distributionName": "Lognormal",
+      "parameters": {
+        "mu": 9.2,
+        "sigma": 0.4
+      }
+    },
+    {
+      "sheetName": "Product Launch Model",
+      "cellAddress": "B10",
+      "label": "Defect Rate",
+      "distributionName": "Beta",
+      "parameters": {
+        "alpha": 2,
+        "beta": 50
+      }
+    },
+    {
+      "sheetName": "Product Launch Model",
+      "cellAddress": "B9",
+      "label": "Marketing Spend ($)",
+      "distributionName": "PERT",
+      "parameters": {
+        "min": 50000,
+        "mode": 80000,
+        "max": 150000
+      }
     }
   ],
-  "outputs": [],
+  "outputs": [
+    {
+      "sheetName": "Product Launch Model",
+      "cellAddress": "B28",
+      "label": "Net Profit ($)"
+    },
+    {
+      "sheetName": "Product Launch Model",
+      "cellAddress": "B30",
+      "label": "Break-Even Units"
+    },
+    {
+      "sheetName": "Product Launch Model",
+      "cellAddress": "B29",
+      "label": "ROI (%)"
+    }
+  ],
   "correlationMatrix": null,
   "correlationMatrixSize": 0
 }]]></Profile>
@@ -1058,7 +3383,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C7C59C8-27A6-46D1-83E3-1118511AB68E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAC7D55A-E610-4AC5-B851-01F3443A032C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="urn:montecarlo-xl:config:v1"/>
   </ds:schemaRefs>
